--- a/output/daily_ratings/uk_ratings_2026-04-20.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-04-20.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P125"/>
+  <dimension ref="A1:P202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3955,51 +3955,51 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>6.004545454545455</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Vollering (IRE)</t>
+          <t>The Gay Blade</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J60" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>58.28</v>
+        <v>72.03</v>
       </c>
       <c r="N60" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4013,53 +4013,53 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>6.004545454545455</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G61" t="n">
         <v>2</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Angel Footsteps</t>
+          <t>Fircombe Hall</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J61" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="L61" t="n">
-        <v>2.5</v>
+        <v>0.15</v>
       </c>
       <c r="M61" t="n">
-        <v>58.28</v>
+        <v>72.03</v>
       </c>
       <c r="N61" t="n">
-        <v>64.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4067,59 +4067,59 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>6.004545454545455</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G62" t="n">
         <v>3</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Cailin Aine (IRE)</t>
+          <t>Asadjumeirah</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J62" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L62" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="M62" t="n">
-        <v>58.28</v>
+        <v>72.03</v>
       </c>
       <c r="N62" t="n">
-        <v>63.5</v>
+        <v>58.3</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4133,53 +4133,53 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>6.004545454545455</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G63" t="n">
         <v>4</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Miss Lizzy</t>
+          <t>Auntie Jo</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J63" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="L63" t="n">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="M63" t="n">
-        <v>58.28</v>
+        <v>72.03</v>
       </c>
       <c r="N63" t="n">
-        <v>66.5</v>
+        <v>59.4</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4187,59 +4187,59 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>6.004545454545455</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G64" t="n">
         <v>5</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Cheeky Chesca (IRE)</t>
+          <t>Quercus (IRE)</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J64" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="L64" t="n">
-        <v>4.93</v>
+        <v>3.9</v>
       </c>
       <c r="M64" t="n">
-        <v>58.28</v>
+        <v>72.03</v>
       </c>
       <c r="N64" t="n">
-        <v>54.7</v>
+        <v>57</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4253,53 +4253,53 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>6.004545454545455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G65" t="n">
         <v>6</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Wopbopaloomop</t>
+          <t>Bernie The Bear (IRE)</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J65" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L65" t="n">
-        <v>5.03</v>
+        <v>5.4</v>
       </c>
       <c r="M65" t="n">
-        <v>58.28</v>
+        <v>72.03</v>
       </c>
       <c r="N65" t="n">
-        <v>53.7</v>
+        <v>44.3</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4313,53 +4313,53 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>6.004545454545455</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G66" t="n">
         <v>7</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Arcadian Days</t>
+          <t>Indys Angel</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L66" t="n">
-        <v>6.28</v>
+        <v>6.15</v>
       </c>
       <c r="M66" t="n">
-        <v>58.28</v>
+        <v>72.03</v>
       </c>
       <c r="N66" t="n">
-        <v>46.1</v>
+        <v>43.2</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4367,59 +4367,59 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>6.004545454545455</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G67" t="n">
         <v>8</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>State of Gold (IRE)</t>
+          <t>Nazca</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J67" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L67" t="n">
-        <v>9.280000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="M67" t="n">
-        <v>58.28</v>
+        <v>72.03</v>
       </c>
       <c r="N67" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4427,59 +4427,59 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>6.004545454545455</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G68" t="n">
         <v>9</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Bea Kindly</t>
+          <t>Gimmieminnie (IRE)</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J68" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L68" t="n">
-        <v>10.28</v>
+        <v>7.7</v>
       </c>
       <c r="M68" t="n">
-        <v>58.28</v>
+        <v>72.03</v>
       </c>
       <c r="N68" t="n">
-        <v>32.9</v>
+        <v>37.4</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4487,113 +4487,119 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>7.995454545454545</v>
+        <v>6.004545454545455</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>6</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Fickle Mcselfish</t>
+          <t>Sedgemoor (IRE)</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
         <v>135</v>
       </c>
       <c r="K69" t="n">
-        <v>60</v>
-      </c>
-      <c r="L69" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="L69" t="n">
+        <v>7.85</v>
+      </c>
       <c r="M69" t="n">
-        <v>97.06999999999999</v>
-      </c>
-      <c r="N69" t="inlineStr"/>
+        <v>72.03</v>
+      </c>
+      <c r="N69" t="n">
+        <v>43.5</v>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>-13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>7.995454545454545</v>
+        <v>6.004545454545455</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>6</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Wild Thoughts (IRE)</t>
+          <t>World Of Darcy (IRE)</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J70" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="K70" t="n">
-        <v>56</v>
-      </c>
-      <c r="L70" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="L70" t="n">
+        <v>8.85</v>
+      </c>
       <c r="M70" t="n">
-        <v>97.06999999999999</v>
+        <v>72.03</v>
       </c>
       <c r="N70" t="n">
-        <v>75.90000000000001</v>
+        <v>33.5</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4607,53 +4613,51 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>2</v>
       </c>
       <c r="C71" t="n">
-        <v>7.995454545454545</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Worlington</t>
+          <t>Analogical</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K71" t="n">
-        <v>56</v>
-      </c>
-      <c r="L71" t="n">
-        <v>4.25</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
-        <v>97.06999999999999</v>
+        <v>160.1</v>
       </c>
       <c r="N71" t="n">
-        <v>66.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -4667,53 +4671,53 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>7.995454545454545</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Harswell River (IRE)</t>
+          <t>Patrol (IRE)</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K72" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="L72" t="n">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="M72" t="n">
-        <v>97.06999999999999</v>
+        <v>160.1</v>
       </c>
       <c r="N72" t="n">
-        <v>58.2</v>
+        <v>65.2</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -4721,59 +4725,59 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>7.995454545454545</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Dalamara</t>
+          <t>Clansman</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J73" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K73" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="L73" t="n">
-        <v>4.9</v>
+        <v>6.25</v>
       </c>
       <c r="M73" t="n">
-        <v>97.06999999999999</v>
+        <v>160.1</v>
       </c>
       <c r="N73" t="n">
-        <v>66.2</v>
+        <v>55</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -4781,59 +4785,59 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>2</v>
       </c>
       <c r="C74" t="n">
-        <v>7.995454545454545</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Resdev Time</t>
+          <t>Mao Shang Wong (IRE)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K74" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="L74" t="n">
-        <v>7.65</v>
+        <v>12.25</v>
       </c>
       <c r="M74" t="n">
-        <v>97.06999999999999</v>
+        <v>160.1</v>
       </c>
       <c r="N74" t="n">
-        <v>58.1</v>
+        <v>50.6</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -4847,57 +4851,57 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>7.995454545454545</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Mereside Princess (IRE)</t>
+          <t>Roger Henry (IRE)</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J75" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K75" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="L75" t="n">
-        <v>7.75</v>
+        <v>33.25</v>
       </c>
       <c r="M75" t="n">
-        <v>97.06999999999999</v>
+        <v>160.1</v>
       </c>
       <c r="N75" t="n">
-        <v>51.9</v>
+        <v>19.7</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -4907,113 +4911,111 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>7.995454545454545</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Hood Wink</t>
+          <t>Moon Sniper</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K76" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="L76" t="n">
-        <v>9.75</v>
+        <v>82.25</v>
       </c>
       <c r="M76" t="n">
-        <v>97.06999999999999</v>
+        <v>160.1</v>
       </c>
       <c r="N76" t="n">
-        <v>44</v>
+        <v>-35.1</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C77" t="n">
-        <v>7.995454545454545</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G77" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Battenburg Belle (IRE)</t>
+          <t>Bintaziza (IRE)</t>
         </is>
       </c>
       <c r="I77" t="n">
         <v>3</v>
       </c>
       <c r="J77" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K77" t="n">
-        <v>50</v>
-      </c>
-      <c r="L77" t="n">
-        <v>10.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>97.06999999999999</v>
+        <v>98.72</v>
       </c>
       <c r="N77" t="n">
-        <v>42</v>
+        <v>78.2</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -5021,59 +5023,59 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C78" t="n">
+        <v>8.022727272727273</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>5</v>
+      </c>
+      <c r="G78" t="n">
         <v>2</v>
       </c>
-      <c r="C78" t="n">
-        <v>7.995454545454545</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Good To Firm</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>6</v>
-      </c>
-      <c r="G78" t="n">
-        <v>9</v>
-      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Amazing Anita</t>
+          <t>Ziata</t>
         </is>
       </c>
       <c r="I78" t="n">
         <v>3</v>
       </c>
       <c r="J78" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K78" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>11.75</v>
+        <v>6.5</v>
       </c>
       <c r="M78" t="n">
-        <v>97.06999999999999</v>
+        <v>98.72</v>
       </c>
       <c r="N78" t="n">
-        <v>47.7</v>
+        <v>62.3</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -5081,59 +5083,59 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79" t="n">
-        <v>7.995454545454545</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G79" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Hear The Drums</t>
+          <t>Mimis Magic</t>
         </is>
       </c>
       <c r="I79" t="n">
         <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="K79" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="L79" t="n">
-        <v>16.5</v>
+        <v>8.25</v>
       </c>
       <c r="M79" t="n">
-        <v>97.06999999999999</v>
+        <v>98.72</v>
       </c>
       <c r="N79" t="n">
-        <v>33.1</v>
+        <v>56.3</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -5141,63 +5143,63 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>7.995454545454545</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G80" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Itszaboy</t>
+          <t>Clocker</t>
         </is>
       </c>
       <c r="I80" t="n">
         <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K80" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>20.25</v>
+        <v>8.35</v>
       </c>
       <c r="M80" t="n">
-        <v>97.06999999999999</v>
+        <v>98.72</v>
       </c>
       <c r="N80" t="n">
-        <v>41.9</v>
+        <v>57.5</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -5207,111 +5209,113 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>7.995454545454545</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G81" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Princess Coco</t>
+          <t>Ice Show</t>
         </is>
       </c>
       <c r="I81" t="n">
         <v>3</v>
       </c>
       <c r="J81" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K81" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>20.4</v>
+        <v>10.85</v>
       </c>
       <c r="M81" t="n">
-        <v>97.06999999999999</v>
+        <v>98.72</v>
       </c>
       <c r="N81" t="n">
-        <v>33.7</v>
+        <v>50.8</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Looks Fantastic</t>
+          <t>Crown Of Dreams</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K82" t="n">
-        <v>60</v>
-      </c>
-      <c r="L82" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>13.1</v>
+      </c>
       <c r="M82" t="n">
-        <v>83.78</v>
+        <v>98.72</v>
       </c>
       <c r="N82" t="n">
-        <v>73.59999999999999</v>
+        <v>45.7</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -5325,53 +5329,53 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>3</v>
       </c>
       <c r="C83" t="n">
+        <v>8.022727272727273</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>5</v>
+      </c>
+      <c r="G83" t="n">
         <v>7</v>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Good To Firm</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>6</v>
-      </c>
-      <c r="G83" t="n">
-        <v>2</v>
-      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Perfidia (IRE)</t>
+          <t>Astrid (FR)</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K83" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>1.25</v>
+        <v>14.6</v>
       </c>
       <c r="M83" t="n">
-        <v>83.78</v>
+        <v>98.72</v>
       </c>
       <c r="N83" t="n">
-        <v>67.3</v>
+        <v>42.4</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -5385,53 +5389,53 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>3</v>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Mayo County</t>
+          <t>Sottna</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="K84" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>2.75</v>
+        <v>17.6</v>
       </c>
       <c r="M84" t="n">
-        <v>83.78</v>
+        <v>98.72</v>
       </c>
       <c r="N84" t="n">
-        <v>66.40000000000001</v>
+        <v>33.6</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -5439,59 +5443,59 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>3</v>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G85" t="n">
+        <v>9</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Beat The Odds</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
         <v>4</v>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>One Of Our Own</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
-        <v>6</v>
-      </c>
       <c r="J85" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="K85" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>4.25</v>
+        <v>18.85</v>
       </c>
       <c r="M85" t="n">
-        <v>83.78</v>
+        <v>98.72</v>
       </c>
       <c r="N85" t="n">
-        <v>58.6</v>
+        <v>34.8</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -5499,123 +5503,123 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>3</v>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Elettaria (IRE)</t>
+          <t>Luscious Lil</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="K86" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>4.3</v>
+        <v>26.35</v>
       </c>
       <c r="M86" t="n">
-        <v>83.78</v>
+        <v>98.72</v>
       </c>
       <c r="N86" t="n">
-        <v>48.8</v>
+        <v>24.8</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>3</v>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Tickets</t>
+          <t>Bridgefoot Rambler</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J87" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="K87" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>4.4</v>
+        <v>26.85</v>
       </c>
       <c r="M87" t="n">
-        <v>83.78</v>
+        <v>98.72</v>
       </c>
       <c r="N87" t="n">
-        <v>53.4</v>
+        <v>25.1</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -5625,113 +5629,103 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>3</v>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>6</v>
-      </c>
-      <c r="G88" t="n">
-        <v>7</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Flying Star (IRE)</t>
+          <t>The Bitters</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="K88" t="n">
-        <v>46</v>
-      </c>
-      <c r="L88" t="n">
-        <v>4.55</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
-        <v>83.78</v>
-      </c>
-      <c r="N88" t="n">
-        <v>47.1</v>
-      </c>
+        <v>98.72</v>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P88" t="n">
-        <v>-3</v>
-      </c>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Woodrafff</t>
+          <t>Gouken (FR)</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="K89" t="n">
-        <v>51</v>
-      </c>
-      <c r="L89" t="n">
-        <v>5.8</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="n">
-        <v>83.78</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="N89" t="n">
-        <v>47.6</v>
+        <v>59</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -5739,59 +5733,59 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Little Ted</t>
+          <t>Kilfrush Desert (IRE)</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="K90" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="M90" t="n">
-        <v>83.78</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="N90" t="n">
-        <v>50.8</v>
+        <v>54.4</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -5799,59 +5793,59 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G91" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Electric Lightning</t>
+          <t>Nebulon (IRE)</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K91" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>7.05</v>
+        <v>3.25</v>
       </c>
       <c r="M91" t="n">
-        <v>83.78</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="N91" t="n">
-        <v>51.5</v>
+        <v>49.4</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -5859,59 +5853,59 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C92" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Without Delay (IRE)</t>
+          <t>Masai Angel (FR)</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="K92" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>8.050000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="M92" t="n">
-        <v>83.78</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="N92" t="n">
-        <v>42.7</v>
+        <v>48.7</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -5925,53 +5919,53 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C93" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G93" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Shes A Goldigger</t>
+          <t>Slot</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="K93" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>8.550000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="M93" t="n">
-        <v>83.78</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="N93" t="n">
-        <v>37.4</v>
+        <v>42.5</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -5979,59 +5973,59 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G94" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Angel Of England</t>
+          <t>Likeadyinwasp (IRE)</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J94" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K94" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>11.05</v>
+        <v>5.5</v>
       </c>
       <c r="M94" t="n">
-        <v>83.78</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="N94" t="n">
-        <v>39.2</v>
+        <v>40</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -6039,59 +6033,59 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C95" t="n">
+        <v>6</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>4</v>
+      </c>
+      <c r="G95" t="n">
         <v>7</v>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Good To Firm</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>6</v>
-      </c>
-      <c r="G95" t="n">
-        <v>14</v>
-      </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Far Ahead (IRE)</t>
+          <t>April Diamond (IRE)</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="K95" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>11.8</v>
+        <v>5.6</v>
       </c>
       <c r="M95" t="n">
-        <v>83.78</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="N95" t="n">
-        <v>35.5</v>
+        <v>37.4</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -6099,57 +6093,59 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>4</v>
       </c>
       <c r="C96" t="n">
-        <v>7.995454545454545</v>
+        <v>6</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Skipper</t>
+          <t>Lindoro</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J96" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="K96" t="n">
-        <v>88</v>
-      </c>
-      <c r="L96" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>6.1</v>
+      </c>
       <c r="M96" t="n">
-        <v>95.06999999999999</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="N96" t="n">
-        <v>80.40000000000001</v>
+        <v>37.4</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -6157,59 +6153,59 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>4</v>
       </c>
       <c r="C97" t="n">
-        <v>7.995454545454545</v>
+        <v>6</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Jolly Roger (IRE)</t>
+          <t>Alfa Impulsion</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="K97" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0.5</v>
+        <v>11.1</v>
       </c>
       <c r="M97" t="n">
-        <v>95.06999999999999</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="N97" t="n">
-        <v>80</v>
+        <v>17.7</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -6217,59 +6213,57 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C98" t="n">
-        <v>7.995454545454545</v>
+        <v>5</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>New Image</t>
+          <t>Enter Sandman (IRE)</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K98" t="n">
-        <v>90</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0.65</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="n">
-        <v>95.06999999999999</v>
+        <v>59.21</v>
       </c>
       <c r="N98" t="n">
-        <v>80</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -6277,59 +6271,59 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C99" t="n">
-        <v>7.995454545454545</v>
+        <v>5</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Seagolazo (IRE)</t>
+          <t>Nanas Boy George (IRE)</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K99" t="n">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="L99" t="n">
-        <v>1.65</v>
+        <v>0.03</v>
       </c>
       <c r="M99" t="n">
-        <v>95.06999999999999</v>
+        <v>59.21</v>
       </c>
       <c r="N99" t="n">
-        <v>74.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -6343,53 +6337,53 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C100" t="n">
-        <v>7.995454545454545</v>
+        <v>5</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Cadarn (IRE)</t>
+          <t>Fille Unique (IRE)</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J100" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K100" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="L100" t="n">
-        <v>4.65</v>
+        <v>0.18</v>
       </c>
       <c r="M100" t="n">
-        <v>95.06999999999999</v>
+        <v>59.21</v>
       </c>
       <c r="N100" t="n">
-        <v>66.7</v>
+        <v>69.8</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -6397,59 +6391,59 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B101" t="n">
+        <v>5</v>
+      </c>
+      <c r="C101" t="n">
+        <v>5</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>6</v>
+      </c>
+      <c r="G101" t="n">
         <v>4</v>
       </c>
-      <c r="C101" t="n">
-        <v>7.995454545454545</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Good To Firm</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>3</v>
-      </c>
-      <c r="G101" t="n">
-        <v>6</v>
-      </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Diderot</t>
+          <t>Golden Havana (IRE)</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J101" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K101" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="L101" t="n">
-        <v>4.8</v>
+        <v>0.28</v>
       </c>
       <c r="M101" t="n">
-        <v>95.06999999999999</v>
+        <v>59.21</v>
       </c>
       <c r="N101" t="n">
-        <v>60.8</v>
+        <v>66.8</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -6463,53 +6457,53 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C102" t="n">
-        <v>7.995454545454545</v>
+        <v>5</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G102" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Double Parked (IRE)</t>
+          <t>Data Fata Secutus</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K102" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="L102" t="n">
-        <v>6.05</v>
+        <v>0.43</v>
       </c>
       <c r="M102" t="n">
-        <v>95.06999999999999</v>
+        <v>59.21</v>
       </c>
       <c r="N102" t="n">
-        <v>57.2</v>
+        <v>63.8</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -6523,53 +6517,53 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C103" t="n">
-        <v>7.995454545454545</v>
+        <v>5</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G103" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sea Legend (FR)</t>
+          <t>Territorial Star</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J103" t="n">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="K103" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="L103" t="n">
-        <v>6.2</v>
+        <v>2.93</v>
       </c>
       <c r="M103" t="n">
-        <v>95.06999999999999</v>
+        <v>59.21</v>
       </c>
       <c r="N103" t="n">
-        <v>47.8</v>
+        <v>60.9</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -6583,53 +6577,53 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C104" t="n">
-        <v>7.995454545454545</v>
+        <v>5</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G104" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Intrusively</t>
+          <t>Perfect Price (IRE)</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J104" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K104" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="L104" t="n">
-        <v>14.7</v>
+        <v>3.08</v>
       </c>
       <c r="M104" t="n">
-        <v>95.06999999999999</v>
+        <v>59.21</v>
       </c>
       <c r="N104" t="n">
-        <v>39.2</v>
+        <v>59.5</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -6643,51 +6637,53 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>5</v>
       </c>
       <c r="C105" t="n">
-        <v>10.00454545454545</v>
+        <v>5</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Mr Colonel (IRE)</t>
+          <t>Jane Of The Jungle (IRE)</t>
         </is>
       </c>
       <c r="I105" t="n">
         <v>3</v>
       </c>
       <c r="J105" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K105" t="n">
-        <v>97</v>
-      </c>
-      <c r="L105" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="L105" t="n">
+        <v>4.33</v>
+      </c>
       <c r="M105" t="n">
-        <v>126.36</v>
+        <v>59.21</v>
       </c>
       <c r="N105" t="n">
-        <v>61.6</v>
+        <v>49.9</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -6695,59 +6691,59 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>5</v>
       </c>
       <c r="C106" t="n">
-        <v>10.00454545454545</v>
+        <v>5</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>According To Mark (IRE)</t>
+          <t>O Fortuna</t>
         </is>
       </c>
       <c r="I106" t="n">
         <v>3</v>
       </c>
       <c r="J106" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L106" t="n">
-        <v>0.05</v>
+        <v>6.33</v>
       </c>
       <c r="M106" t="n">
-        <v>126.36</v>
+        <v>59.21</v>
       </c>
       <c r="N106" t="n">
-        <v>61.9</v>
+        <v>46.3</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -6755,40 +6751,40 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>5</v>
       </c>
       <c r="C107" t="n">
-        <v>10.00454545454545</v>
+        <v>5</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G107" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Bay Of Myths (IRE)</t>
+          <t>Bella Delizia</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -6798,16 +6794,16 @@
         <v>133</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="L107" t="n">
-        <v>7.05</v>
+        <v>12.33</v>
       </c>
       <c r="M107" t="n">
-        <v>126.36</v>
+        <v>59.21</v>
       </c>
       <c r="N107" t="n">
-        <v>50.4</v>
+        <v>25.9</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -6821,57 +6817,57 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>5</v>
       </c>
       <c r="C108" t="n">
-        <v>10.00454545454545</v>
+        <v>5</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G108" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Heathers Feather (IRE)</t>
+          <t>Regal Dream</t>
         </is>
       </c>
       <c r="I108" t="n">
         <v>3</v>
       </c>
       <c r="J108" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L108" t="n">
-        <v>26.05</v>
+        <v>19.33</v>
       </c>
       <c r="M108" t="n">
-        <v>126.36</v>
+        <v>59.21</v>
       </c>
       <c r="N108" t="n">
-        <v>21.7</v>
+        <v>-12.4</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -6881,23 +6877,23 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>6</v>
       </c>
       <c r="C109" t="n">
-        <v>10.00454545454545</v>
+        <v>7.068181818181818</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -6908,24 +6904,24 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Mafting</t>
+          <t>Lord Capulet (IRE)</t>
         </is>
       </c>
       <c r="I109" t="n">
         <v>4</v>
       </c>
       <c r="J109" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K109" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
-        <v>125.67</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N109" t="n">
-        <v>73</v>
+        <v>78.3</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -6933,29 +6929,29 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>6</v>
       </c>
       <c r="C110" t="n">
-        <v>10.00454545454545</v>
+        <v>7.068181818181818</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -6966,26 +6962,26 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Urban Road</t>
+          <t>The Green Man (IRE)</t>
         </is>
       </c>
       <c r="I110" t="n">
         <v>7</v>
       </c>
       <c r="J110" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K110" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L110" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="M110" t="n">
-        <v>125.67</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N110" t="n">
-        <v>67.09999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -6993,29 +6989,29 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B111" t="n">
         <v>6</v>
       </c>
       <c r="C111" t="n">
-        <v>10.00454545454545</v>
+        <v>7.068181818181818</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -7026,26 +7022,26 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Imperial Trooper (IRE)</t>
+          <t>Kings School</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J111" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K111" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L111" t="n">
-        <v>2.75</v>
+        <v>0.65</v>
       </c>
       <c r="M111" t="n">
-        <v>125.67</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N111" t="n">
-        <v>63.9</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -7053,29 +7049,29 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B112" t="n">
         <v>6</v>
       </c>
       <c r="C112" t="n">
-        <v>10.00454545454545</v>
+        <v>7.068181818181818</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -7086,26 +7082,26 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Nicator (FR)</t>
+          <t>Ziggys Condor (IRE)</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J112" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K112" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L112" t="n">
-        <v>4.25</v>
+        <v>2.15</v>
       </c>
       <c r="M112" t="n">
-        <v>125.67</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N112" t="n">
-        <v>63.1</v>
+        <v>76.5</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -7119,23 +7115,23 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B113" t="n">
         <v>6</v>
       </c>
       <c r="C113" t="n">
-        <v>10.00454545454545</v>
+        <v>7.068181818181818</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -7146,26 +7142,26 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Not Me</t>
+          <t>Criminal Shore (IRE)</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J113" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K113" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L113" t="n">
-        <v>4.35</v>
+        <v>2.2</v>
       </c>
       <c r="M113" t="n">
-        <v>125.67</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N113" t="n">
-        <v>60.9</v>
+        <v>75.5</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -7179,23 +7175,23 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B114" t="n">
         <v>6</v>
       </c>
       <c r="C114" t="n">
-        <v>10.00454545454545</v>
+        <v>7.068181818181818</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -7206,26 +7202,26 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Dawn Of Liberation (IRE)</t>
+          <t>Anthropologist</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J114" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K114" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L114" t="n">
-        <v>4.5</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="M114" t="n">
-        <v>125.67</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N114" t="n">
-        <v>60.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -7239,23 +7235,23 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>6</v>
       </c>
       <c r="C115" t="n">
-        <v>10.00454545454545</v>
+        <v>7.068181818181818</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -7266,26 +7262,26 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Jam Lass</t>
+          <t>Phoenix Of Dreams (IRE)</t>
         </is>
       </c>
       <c r="I115" t="n">
         <v>5</v>
       </c>
       <c r="J115" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K115" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L115" t="n">
-        <v>8.75</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="M115" t="n">
-        <v>125.67</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N115" t="n">
-        <v>43.6</v>
+        <v>60.3</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -7293,29 +7289,29 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B116" t="n">
         <v>6</v>
       </c>
       <c r="C116" t="n">
-        <v>10.00454545454545</v>
+        <v>7.068181818181818</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -7326,26 +7322,26 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Character Testing</t>
+          <t>Novak</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J116" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K116" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L116" t="n">
-        <v>10</v>
+        <v>5.85</v>
       </c>
       <c r="M116" t="n">
-        <v>125.67</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N116" t="n">
-        <v>43.6</v>
+        <v>59.4</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -7353,29 +7349,29 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>6</v>
       </c>
       <c r="C117" t="n">
-        <v>10.00454545454545</v>
+        <v>7.068181818181818</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -7386,26 +7382,26 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Hill O Rue</t>
+          <t>Blazing Son</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J117" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K117" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="L117" t="n">
-        <v>10.15</v>
+        <v>5.899999999999999</v>
       </c>
       <c r="M117" t="n">
-        <v>125.67</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N117" t="n">
-        <v>39.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -7413,57 +7409,59 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C118" t="n">
-        <v>5.986363636363636</v>
+        <v>7.068181818181818</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Watchdog</t>
+          <t>Bobby Joe Leg</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J118" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="K118" t="n">
-        <v>65</v>
-      </c>
-      <c r="L118" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="L118" t="n">
+        <v>7.149999999999999</v>
+      </c>
       <c r="M118" t="n">
-        <v>71.28</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N118" t="n">
-        <v>73.2</v>
+        <v>55.4</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -7477,53 +7475,53 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B119" t="n">
+        <v>6</v>
+      </c>
+      <c r="C119" t="n">
+        <v>7.068181818181818</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>5</v>
+      </c>
+      <c r="G119" t="n">
+        <v>11</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kitaab</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
         <v>7</v>
       </c>
-      <c r="C119" t="n">
-        <v>5.986363636363636</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Good To Firm</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>6</v>
-      </c>
-      <c r="G119" t="n">
-        <v>2</v>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Gunalt Wavelength</t>
-        </is>
-      </c>
-      <c r="I119" t="n">
-        <v>3</v>
-      </c>
       <c r="J119" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="K119" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L119" t="n">
-        <v>1.5</v>
+        <v>9.649999999999999</v>
       </c>
       <c r="M119" t="n">
-        <v>71.28</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N119" t="n">
-        <v>62.5</v>
+        <v>42.2</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -7531,59 +7529,59 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C120" t="n">
-        <v>5.986363636363636</v>
+        <v>7.068181818181818</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G120" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Long Shot</t>
+          <t>Cusack</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J120" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K120" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="L120" t="n">
-        <v>1.53</v>
+        <v>10.15</v>
       </c>
       <c r="M120" t="n">
-        <v>71.28</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N120" t="n">
-        <v>57.3</v>
+        <v>45.2</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -7591,59 +7589,59 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C121" t="n">
-        <v>5.986363636363636</v>
+        <v>7.068181818181818</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G121" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Belling The Cat</t>
+          <t>Too Much</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J121" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K121" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="L121" t="n">
-        <v>3.28</v>
+        <v>17.15</v>
       </c>
       <c r="M121" t="n">
-        <v>71.28</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N121" t="n">
-        <v>49.3</v>
+        <v>27.1</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -7651,59 +7649,59 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C122" t="n">
-        <v>5.986363636363636</v>
+        <v>7.068181818181818</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G122" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Auspicious</t>
+          <t>Call Me Betty (IRE)</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J122" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="K122" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L122" t="n">
-        <v>6.53</v>
+        <v>18.9</v>
       </c>
       <c r="M122" t="n">
-        <v>71.28</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N122" t="n">
-        <v>39.5</v>
+        <v>32.8</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -7711,59 +7709,57 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>7</v>
       </c>
       <c r="C123" t="n">
-        <v>5.986363636363636</v>
+        <v>8.027272727272727</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F123" t="n">
         <v>6</v>
       </c>
       <c r="G123" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Mystical Land (IRE)</t>
+          <t>Esque Elegance (IRE)</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J123" t="n">
         <v>128</v>
       </c>
       <c r="K123" t="n">
-        <v>58</v>
-      </c>
-      <c r="L123" t="n">
-        <v>7.03</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
       <c r="M123" t="n">
-        <v>71.28</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="N123" t="n">
-        <v>44.2</v>
+        <v>64.3</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -7771,59 +7767,59 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>7</v>
       </c>
       <c r="C124" t="n">
-        <v>5.986363636363636</v>
+        <v>8.027272727272727</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F124" t="n">
         <v>6</v>
       </c>
       <c r="G124" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Muvable</t>
+          <t>Take The A Train</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J124" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="K124" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L124" t="n">
-        <v>12.03</v>
+        <v>1.25</v>
       </c>
       <c r="M124" t="n">
-        <v>71.28</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="N124" t="n">
-        <v>20.1</v>
+        <v>62</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -7831,66 +7827,4668 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>REDCAR</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>7</v>
       </c>
       <c r="C125" t="n">
+        <v>8.027272727272727</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>6</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Cloch Nua</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>7</v>
+      </c>
+      <c r="J125" t="n">
+        <v>134</v>
+      </c>
+      <c r="K125" t="n">
+        <v>54</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M125" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="N125" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>7</v>
+      </c>
+      <c r="C126" t="n">
+        <v>8.027272727272727</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>6</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Teggy Lasso (IRE)</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>4</v>
+      </c>
+      <c r="J126" t="n">
+        <v>135</v>
+      </c>
+      <c r="K126" t="n">
+        <v>55</v>
+      </c>
+      <c r="L126" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M126" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="N126" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>7</v>
+      </c>
+      <c r="C127" t="n">
+        <v>8.027272727272727</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>6</v>
+      </c>
+      <c r="G127" t="n">
+        <v>5</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Top Gun Tina</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>6</v>
+      </c>
+      <c r="J127" t="n">
+        <v>126</v>
+      </c>
+      <c r="K127" t="n">
+        <v>46</v>
+      </c>
+      <c r="L127" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M127" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="N127" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>7</v>
+      </c>
+      <c r="C128" t="n">
+        <v>8.027272727272727</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>6</v>
+      </c>
+      <c r="G128" t="n">
+        <v>6</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Misemerald (IRE)</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>5</v>
+      </c>
+      <c r="J128" t="n">
+        <v>129</v>
+      </c>
+      <c r="K128" t="n">
+        <v>49</v>
+      </c>
+      <c r="L128" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="M128" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="N128" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>7</v>
+      </c>
+      <c r="C129" t="n">
+        <v>8.027272727272727</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>6</v>
+      </c>
+      <c r="G129" t="n">
+        <v>7</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Martins Brig (IRE)</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>9</v>
+      </c>
+      <c r="J129" t="n">
+        <v>126</v>
+      </c>
+      <c r="K129" t="n">
+        <v>46</v>
+      </c>
+      <c r="L129" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M129" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="N129" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>7</v>
+      </c>
+      <c r="C130" t="n">
+        <v>8.027272727272727</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>6</v>
+      </c>
+      <c r="G130" t="n">
+        <v>8</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Trais Fluors</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>12</v>
+      </c>
+      <c r="J130" t="n">
+        <v>134</v>
+      </c>
+      <c r="K130" t="n">
+        <v>54</v>
+      </c>
+      <c r="L130" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="M130" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="N130" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>7</v>
+      </c>
+      <c r="C131" t="n">
+        <v>8.027272727272727</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>6</v>
+      </c>
+      <c r="G131" t="n">
+        <v>9</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Bitacora (IRE)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>6</v>
+      </c>
+      <c r="J131" t="n">
+        <v>129</v>
+      </c>
+      <c r="K131" t="n">
+        <v>49</v>
+      </c>
+      <c r="L131" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="M131" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="N131" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>7</v>
+      </c>
+      <c r="C132" t="n">
+        <v>8.027272727272727</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>6</v>
+      </c>
+      <c r="G132" t="n">
+        <v>10</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Wheres The Crumpet</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>8</v>
+      </c>
+      <c r="J132" t="n">
+        <v>127</v>
+      </c>
+      <c r="K132" t="n">
+        <v>47</v>
+      </c>
+      <c r="L132" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="M132" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="N132" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>7</v>
+      </c>
+      <c r="C133" t="n">
+        <v>8.027272727272727</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>6</v>
+      </c>
+      <c r="G133" t="n">
+        <v>11</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Ridgemaster (IRE)</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>4</v>
+      </c>
+      <c r="J133" t="n">
+        <v>132</v>
+      </c>
+      <c r="K133" t="n">
+        <v>52</v>
+      </c>
+      <c r="L133" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="M133" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="N133" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>7</v>
+      </c>
+      <c r="C134" t="n">
+        <v>8.027272727272727</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>6</v>
+      </c>
+      <c r="G134" t="n">
+        <v>12</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Starshot (IRE)</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>6</v>
+      </c>
+      <c r="J134" t="n">
+        <v>129</v>
+      </c>
+      <c r="K134" t="n">
+        <v>49</v>
+      </c>
+      <c r="L134" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="M134" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="N134" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>7</v>
+      </c>
+      <c r="C135" t="n">
+        <v>8.027272727272727</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>6</v>
+      </c>
+      <c r="G135" t="n">
+        <v>13</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Pebble Dash (IRE)</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>4</v>
+      </c>
+      <c r="J135" t="n">
+        <v>129</v>
+      </c>
+      <c r="K135" t="n">
+        <v>49</v>
+      </c>
+      <c r="L135" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="M135" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="N135" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>NEWCASTLE</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>7</v>
+      </c>
+      <c r="C136" t="n">
+        <v>8.027272727272727</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>6</v>
+      </c>
+      <c r="G136" t="n">
+        <v>14</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Tainted Love</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>4</v>
+      </c>
+      <c r="J136" t="n">
+        <v>127</v>
+      </c>
+      <c r="K136" t="n">
+        <v>47</v>
+      </c>
+      <c r="L136" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="M136" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="N136" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" t="n">
+        <v>5</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>5</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Vollering (IRE)</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>2</v>
+      </c>
+      <c r="J137" t="n">
+        <v>128</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="N137" t="n">
+        <v>78</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="n">
+        <v>5</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>5</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Angel Footsteps</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>2</v>
+      </c>
+      <c r="J138" t="n">
+        <v>122</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M138" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="N138" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="n">
+        <v>5</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>5</v>
+      </c>
+      <c r="G139" t="n">
+        <v>3</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Cailin Aine (IRE)</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>2</v>
+      </c>
+      <c r="J139" t="n">
+        <v>122</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M139" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="N139" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" t="n">
+        <v>5</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>5</v>
+      </c>
+      <c r="G140" t="n">
+        <v>4</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Miss Lizzy</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>2</v>
+      </c>
+      <c r="J140" t="n">
+        <v>128</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M140" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="N140" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="n">
+        <v>5</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>5</v>
+      </c>
+      <c r="G141" t="n">
+        <v>5</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Cheeky Chesca (IRE)</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>2</v>
+      </c>
+      <c r="J141" t="n">
+        <v>122</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="M141" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="N141" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="n">
+        <v>5</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>5</v>
+      </c>
+      <c r="G142" t="n">
+        <v>6</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Wopbopaloomop</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>2</v>
+      </c>
+      <c r="J142" t="n">
+        <v>125</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="M142" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="N142" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="n">
+        <v>5</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>5</v>
+      </c>
+      <c r="G143" t="n">
+        <v>7</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Arcadian Days</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>2</v>
+      </c>
+      <c r="J143" t="n">
+        <v>122</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="M143" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="N143" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" t="n">
+        <v>5</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>5</v>
+      </c>
+      <c r="G144" t="n">
+        <v>8</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>State of Gold (IRE)</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>2</v>
+      </c>
+      <c r="J144" t="n">
+        <v>125</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>9.280000000000001</v>
+      </c>
+      <c r="M144" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="N144" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="n">
+        <v>5</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>5</v>
+      </c>
+      <c r="G145" t="n">
+        <v>9</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Bea Kindly</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>2</v>
+      </c>
+      <c r="J145" t="n">
+        <v>125</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="M145" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="N145" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>2</v>
+      </c>
+      <c r="C146" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>6</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Fickle Mcselfish</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>3</v>
+      </c>
+      <c r="J146" t="n">
+        <v>135</v>
+      </c>
+      <c r="K146" t="n">
+        <v>60</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>2</v>
+      </c>
+      <c r="C147" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>6</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Wild Thoughts (IRE)</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>3</v>
+      </c>
+      <c r="J147" t="n">
+        <v>131</v>
+      </c>
+      <c r="K147" t="n">
+        <v>56</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="N147" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>2</v>
+      </c>
+      <c r="C148" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>6</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Worlington</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>3</v>
+      </c>
+      <c r="J148" t="n">
+        <v>131</v>
+      </c>
+      <c r="K148" t="n">
+        <v>56</v>
+      </c>
+      <c r="L148" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M148" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="N148" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2</v>
+      </c>
+      <c r="C149" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>6</v>
+      </c>
+      <c r="G149" t="n">
+        <v>3</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Harswell River (IRE)</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>3</v>
+      </c>
+      <c r="J149" t="n">
+        <v>125</v>
+      </c>
+      <c r="K149" t="n">
+        <v>50</v>
+      </c>
+      <c r="L149" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="M149" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="N149" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>2</v>
+      </c>
+      <c r="C150" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>6</v>
+      </c>
+      <c r="G150" t="n">
+        <v>4</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Dalamara</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>3</v>
+      </c>
+      <c r="J150" t="n">
+        <v>133</v>
+      </c>
+      <c r="K150" t="n">
+        <v>58</v>
+      </c>
+      <c r="L150" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M150" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="N150" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>2</v>
+      </c>
+      <c r="C151" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>6</v>
+      </c>
+      <c r="G151" t="n">
+        <v>5</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Resdev Time</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>3</v>
+      </c>
+      <c r="J151" t="n">
+        <v>132</v>
+      </c>
+      <c r="K151" t="n">
+        <v>57</v>
+      </c>
+      <c r="L151" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="M151" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="N151" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>2</v>
+      </c>
+      <c r="C152" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>6</v>
+      </c>
+      <c r="G152" t="n">
+        <v>6</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Mereside Princess (IRE)</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>3</v>
+      </c>
+      <c r="J152" t="n">
+        <v>126</v>
+      </c>
+      <c r="K152" t="n">
+        <v>51</v>
+      </c>
+      <c r="L152" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="M152" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="N152" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2</v>
+      </c>
+      <c r="C153" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>6</v>
+      </c>
+      <c r="G153" t="n">
+        <v>7</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Hood Wink</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>3</v>
+      </c>
+      <c r="J153" t="n">
+        <v>122</v>
+      </c>
+      <c r="K153" t="n">
+        <v>47</v>
+      </c>
+      <c r="L153" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="M153" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="N153" t="n">
+        <v>44</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>2</v>
+      </c>
+      <c r="C154" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>6</v>
+      </c>
+      <c r="G154" t="n">
+        <v>8</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Battenburg Belle (IRE)</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>3</v>
+      </c>
+      <c r="J154" t="n">
+        <v>125</v>
+      </c>
+      <c r="K154" t="n">
+        <v>50</v>
+      </c>
+      <c r="L154" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="M154" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="N154" t="n">
+        <v>42</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>2</v>
+      </c>
+      <c r="C155" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>6</v>
+      </c>
+      <c r="G155" t="n">
+        <v>9</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Amazing Anita</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>3</v>
+      </c>
+      <c r="J155" t="n">
+        <v>134</v>
+      </c>
+      <c r="K155" t="n">
+        <v>59</v>
+      </c>
+      <c r="L155" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="M155" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="N155" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>2</v>
+      </c>
+      <c r="C156" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>6</v>
+      </c>
+      <c r="G156" t="n">
+        <v>10</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Hear The Drums</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>3</v>
+      </c>
+      <c r="J156" t="n">
+        <v>131</v>
+      </c>
+      <c r="K156" t="n">
+        <v>56</v>
+      </c>
+      <c r="L156" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="M156" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="N156" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2</v>
+      </c>
+      <c r="C157" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>6</v>
+      </c>
+      <c r="G157" t="n">
+        <v>11</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Itszaboy</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>3</v>
+      </c>
+      <c r="J157" t="n">
+        <v>133</v>
+      </c>
+      <c r="K157" t="n">
+        <v>58</v>
+      </c>
+      <c r="L157" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="M157" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="N157" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>2</v>
+      </c>
+      <c r="C158" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>6</v>
+      </c>
+      <c r="G158" t="n">
+        <v>12</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Princess Coco</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>3</v>
+      </c>
+      <c r="J158" t="n">
+        <v>124</v>
+      </c>
+      <c r="K158" t="n">
+        <v>49</v>
+      </c>
+      <c r="L158" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M158" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="N158" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>3</v>
+      </c>
+      <c r="C159" t="n">
+        <v>7</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>6</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Looks Fantastic</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>4</v>
+      </c>
+      <c r="J159" t="n">
+        <v>135</v>
+      </c>
+      <c r="K159" t="n">
+        <v>60</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N159" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>3</v>
+      </c>
+      <c r="C160" t="n">
+        <v>7</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>6</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Perfidia (IRE)</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>4</v>
+      </c>
+      <c r="J160" t="n">
+        <v>131</v>
+      </c>
+      <c r="K160" t="n">
+        <v>56</v>
+      </c>
+      <c r="L160" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M160" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N160" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>3</v>
+      </c>
+      <c r="C161" t="n">
+        <v>7</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>6</v>
+      </c>
+      <c r="G161" t="n">
+        <v>3</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Mayo County</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>5</v>
+      </c>
+      <c r="J161" t="n">
+        <v>134</v>
+      </c>
+      <c r="K161" t="n">
+        <v>59</v>
+      </c>
+      <c r="L161" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M161" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N161" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>3</v>
+      </c>
+      <c r="C162" t="n">
+        <v>7</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>6</v>
+      </c>
+      <c r="G162" t="n">
+        <v>4</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>One Of Our Own</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>6</v>
+      </c>
+      <c r="J162" t="n">
+        <v>130</v>
+      </c>
+      <c r="K162" t="n">
+        <v>55</v>
+      </c>
+      <c r="L162" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M162" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N162" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>3</v>
+      </c>
+      <c r="C163" t="n">
+        <v>7</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>6</v>
+      </c>
+      <c r="G163" t="n">
+        <v>5</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Elettaria (IRE)</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>7</v>
+      </c>
+      <c r="J163" t="n">
+        <v>121</v>
+      </c>
+      <c r="K163" t="n">
+        <v>46</v>
+      </c>
+      <c r="L163" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M163" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N163" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>3</v>
+      </c>
+      <c r="C164" t="n">
+        <v>7</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>6</v>
+      </c>
+      <c r="G164" t="n">
+        <v>6</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Tickets</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>7</v>
+      </c>
+      <c r="J164" t="n">
+        <v>126</v>
+      </c>
+      <c r="K164" t="n">
+        <v>51</v>
+      </c>
+      <c r="L164" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M164" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N164" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>3</v>
+      </c>
+      <c r="C165" t="n">
+        <v>7</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>6</v>
+      </c>
+      <c r="G165" t="n">
+        <v>7</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Flying Star (IRE)</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>6</v>
+      </c>
+      <c r="J165" t="n">
+        <v>121</v>
+      </c>
+      <c r="K165" t="n">
+        <v>46</v>
+      </c>
+      <c r="L165" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="M165" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N165" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>3</v>
+      </c>
+      <c r="C166" t="n">
+        <v>7</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>6</v>
+      </c>
+      <c r="G166" t="n">
+        <v>8</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Woodrafff</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>5</v>
+      </c>
+      <c r="J166" t="n">
+        <v>126</v>
+      </c>
+      <c r="K166" t="n">
+        <v>51</v>
+      </c>
+      <c r="L166" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M166" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N166" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>3</v>
+      </c>
+      <c r="C167" t="n">
+        <v>7</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>6</v>
+      </c>
+      <c r="G167" t="n">
+        <v>9</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Little Ted</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>9</v>
+      </c>
+      <c r="J167" t="n">
+        <v>131</v>
+      </c>
+      <c r="K167" t="n">
+        <v>56</v>
+      </c>
+      <c r="L167" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M167" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N167" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>3</v>
+      </c>
+      <c r="C168" t="n">
+        <v>7</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>6</v>
+      </c>
+      <c r="G168" t="n">
+        <v>10</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Electric Lightning</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>5</v>
+      </c>
+      <c r="J168" t="n">
+        <v>134</v>
+      </c>
+      <c r="K168" t="n">
+        <v>59</v>
+      </c>
+      <c r="L168" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="M168" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N168" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>3</v>
+      </c>
+      <c r="C169" t="n">
+        <v>7</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>6</v>
+      </c>
+      <c r="G169" t="n">
+        <v>11</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Without Delay (IRE)</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>7</v>
+      </c>
+      <c r="J169" t="n">
+        <v>126</v>
+      </c>
+      <c r="K169" t="n">
+        <v>51</v>
+      </c>
+      <c r="L169" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="M169" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N169" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>3</v>
+      </c>
+      <c r="C170" t="n">
+        <v>7</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>6</v>
+      </c>
+      <c r="G170" t="n">
+        <v>12</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Shes A Goldigger</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>4</v>
+      </c>
+      <c r="J170" t="n">
+        <v>121</v>
+      </c>
+      <c r="K170" t="n">
+        <v>46</v>
+      </c>
+      <c r="L170" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="M170" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N170" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>3</v>
+      </c>
+      <c r="C171" t="n">
+        <v>7</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>6</v>
+      </c>
+      <c r="G171" t="n">
+        <v>13</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Angel Of England</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>5</v>
+      </c>
+      <c r="J171" t="n">
+        <v>132</v>
+      </c>
+      <c r="K171" t="n">
+        <v>57</v>
+      </c>
+      <c r="L171" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="M171" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N171" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>3</v>
+      </c>
+      <c r="C172" t="n">
+        <v>7</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>6</v>
+      </c>
+      <c r="G172" t="n">
+        <v>14</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Far Ahead (IRE)</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>4</v>
+      </c>
+      <c r="J172" t="n">
+        <v>129</v>
+      </c>
+      <c r="K172" t="n">
+        <v>54</v>
+      </c>
+      <c r="L172" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M172" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="N172" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>4</v>
+      </c>
+      <c r="C173" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>3</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Skipper</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>5</v>
+      </c>
+      <c r="J173" t="n">
+        <v>133</v>
+      </c>
+      <c r="K173" t="n">
+        <v>88</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="N173" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>4</v>
+      </c>
+      <c r="C174" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>3</v>
+      </c>
+      <c r="G174" t="n">
+        <v>2</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Jolly Roger (IRE)</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>4</v>
+      </c>
+      <c r="J174" t="n">
+        <v>134</v>
+      </c>
+      <c r="K174" t="n">
+        <v>89</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M174" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="N174" t="n">
+        <v>80</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>4</v>
+      </c>
+      <c r="C175" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>3</v>
+      </c>
+      <c r="G175" t="n">
+        <v>3</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>New Image</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>6</v>
+      </c>
+      <c r="J175" t="n">
+        <v>135</v>
+      </c>
+      <c r="K175" t="n">
+        <v>90</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M175" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="N175" t="n">
+        <v>80</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>4</v>
+      </c>
+      <c r="C176" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>3</v>
+      </c>
+      <c r="G176" t="n">
+        <v>4</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Seagolazo (IRE)</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>4</v>
+      </c>
+      <c r="J176" t="n">
+        <v>132</v>
+      </c>
+      <c r="K176" t="n">
+        <v>87</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M176" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="N176" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>4</v>
+      </c>
+      <c r="C177" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>3</v>
+      </c>
+      <c r="G177" t="n">
+        <v>5</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Cadarn (IRE)</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>5</v>
+      </c>
+      <c r="J177" t="n">
+        <v>132</v>
+      </c>
+      <c r="K177" t="n">
+        <v>87</v>
+      </c>
+      <c r="L177" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="M177" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="N177" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>4</v>
+      </c>
+      <c r="C178" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>3</v>
+      </c>
+      <c r="G178" t="n">
+        <v>6</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Diderot</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>8</v>
+      </c>
+      <c r="J178" t="n">
+        <v>126</v>
+      </c>
+      <c r="K178" t="n">
+        <v>81</v>
+      </c>
+      <c r="L178" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M178" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="N178" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>4</v>
+      </c>
+      <c r="C179" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>3</v>
+      </c>
+      <c r="G179" t="n">
+        <v>7</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Double Parked (IRE)</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>4</v>
+      </c>
+      <c r="J179" t="n">
+        <v>126</v>
+      </c>
+      <c r="K179" t="n">
+        <v>81</v>
+      </c>
+      <c r="L179" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="M179" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="N179" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>4</v>
+      </c>
+      <c r="C180" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>3</v>
+      </c>
+      <c r="G180" t="n">
+        <v>8</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sea Legend (FR)</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>6</v>
+      </c>
+      <c r="J180" t="n">
+        <v>116</v>
+      </c>
+      <c r="K180" t="n">
+        <v>71</v>
+      </c>
+      <c r="L180" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M180" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="N180" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>4</v>
+      </c>
+      <c r="C181" t="n">
+        <v>7.995454545454545</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>3</v>
+      </c>
+      <c r="G181" t="n">
+        <v>9</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Intrusively</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>4</v>
+      </c>
+      <c r="J181" t="n">
+        <v>128</v>
+      </c>
+      <c r="K181" t="n">
+        <v>83</v>
+      </c>
+      <c r="L181" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M181" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="N181" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>5</v>
+      </c>
+      <c r="C182" t="n">
+        <v>10.00454545454545</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>3</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Mr Colonel (IRE)</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>3</v>
+      </c>
+      <c r="J182" t="n">
+        <v>126</v>
+      </c>
+      <c r="K182" t="n">
+        <v>97</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="n">
+        <v>126.36</v>
+      </c>
+      <c r="N182" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>5</v>
+      </c>
+      <c r="C183" t="n">
+        <v>10.00454545454545</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>3</v>
+      </c>
+      <c r="G183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>According To Mark (IRE)</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>3</v>
+      </c>
+      <c r="J183" t="n">
+        <v>126</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M183" t="n">
+        <v>126.36</v>
+      </c>
+      <c r="N183" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>5</v>
+      </c>
+      <c r="C184" t="n">
+        <v>10.00454545454545</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>3</v>
+      </c>
+      <c r="G184" t="n">
+        <v>3</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Bay Of Myths (IRE)</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>3</v>
+      </c>
+      <c r="J184" t="n">
+        <v>133</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="M184" t="n">
+        <v>126.36</v>
+      </c>
+      <c r="N184" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>5</v>
+      </c>
+      <c r="C185" t="n">
+        <v>10.00454545454545</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>3</v>
+      </c>
+      <c r="G185" t="n">
+        <v>4</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Heathers Feather (IRE)</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>3</v>
+      </c>
+      <c r="J185" t="n">
+        <v>126</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="M185" t="n">
+        <v>126.36</v>
+      </c>
+      <c r="N185" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>6</v>
+      </c>
+      <c r="C186" t="n">
+        <v>10.00454545454545</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>5</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Mafting</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>4</v>
+      </c>
+      <c r="J186" t="n">
+        <v>135</v>
+      </c>
+      <c r="K186" t="n">
+        <v>75</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="n">
+        <v>125.67</v>
+      </c>
+      <c r="N186" t="n">
+        <v>73</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>6</v>
+      </c>
+      <c r="C187" t="n">
+        <v>10.00454545454545</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>5</v>
+      </c>
+      <c r="G187" t="n">
+        <v>2</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Urban Road</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>7</v>
+      </c>
+      <c r="J187" t="n">
+        <v>132</v>
+      </c>
+      <c r="K187" t="n">
+        <v>72</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M187" t="n">
+        <v>125.67</v>
+      </c>
+      <c r="N187" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>6</v>
+      </c>
+      <c r="C188" t="n">
+        <v>10.00454545454545</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>5</v>
+      </c>
+      <c r="G188" t="n">
+        <v>3</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Imperial Trooper (IRE)</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>4</v>
+      </c>
+      <c r="J188" t="n">
+        <v>131</v>
+      </c>
+      <c r="K188" t="n">
+        <v>71</v>
+      </c>
+      <c r="L188" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M188" t="n">
+        <v>125.67</v>
+      </c>
+      <c r="N188" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>6</v>
+      </c>
+      <c r="C189" t="n">
+        <v>10.00454545454545</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>5</v>
+      </c>
+      <c r="G189" t="n">
+        <v>4</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Nicator (FR)</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>4</v>
+      </c>
+      <c r="J189" t="n">
+        <v>135</v>
+      </c>
+      <c r="K189" t="n">
+        <v>75</v>
+      </c>
+      <c r="L189" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M189" t="n">
+        <v>125.67</v>
+      </c>
+      <c r="N189" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>6</v>
+      </c>
+      <c r="C190" t="n">
+        <v>10.00454545454545</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>5</v>
+      </c>
+      <c r="G190" t="n">
+        <v>5</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Not Me</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>5</v>
+      </c>
+      <c r="J190" t="n">
+        <v>132</v>
+      </c>
+      <c r="K190" t="n">
+        <v>72</v>
+      </c>
+      <c r="L190" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="M190" t="n">
+        <v>125.67</v>
+      </c>
+      <c r="N190" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>6</v>
+      </c>
+      <c r="C191" t="n">
+        <v>10.00454545454545</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>5</v>
+      </c>
+      <c r="G191" t="n">
+        <v>6</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Dawn Of Liberation (IRE)</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>7</v>
+      </c>
+      <c r="J191" t="n">
+        <v>133</v>
+      </c>
+      <c r="K191" t="n">
+        <v>73</v>
+      </c>
+      <c r="L191" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M191" t="n">
+        <v>125.67</v>
+      </c>
+      <c r="N191" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>6</v>
+      </c>
+      <c r="C192" t="n">
+        <v>10.00454545454545</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>5</v>
+      </c>
+      <c r="G192" t="n">
+        <v>7</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Jam Lass</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>5</v>
+      </c>
+      <c r="J192" t="n">
+        <v>123</v>
+      </c>
+      <c r="K192" t="n">
+        <v>63</v>
+      </c>
+      <c r="L192" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M192" t="n">
+        <v>125.67</v>
+      </c>
+      <c r="N192" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>6</v>
+      </c>
+      <c r="C193" t="n">
+        <v>10.00454545454545</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>5</v>
+      </c>
+      <c r="G193" t="n">
+        <v>8</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Character Testing</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>5</v>
+      </c>
+      <c r="J193" t="n">
+        <v>125</v>
+      </c>
+      <c r="K193" t="n">
+        <v>65</v>
+      </c>
+      <c r="L193" t="n">
+        <v>10</v>
+      </c>
+      <c r="M193" t="n">
+        <v>125.67</v>
+      </c>
+      <c r="N193" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>6</v>
+      </c>
+      <c r="C194" t="n">
+        <v>10.00454545454545</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>5</v>
+      </c>
+      <c r="G194" t="n">
+        <v>9</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Hill O Rue</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>4</v>
+      </c>
+      <c r="J194" t="n">
+        <v>124</v>
+      </c>
+      <c r="K194" t="n">
+        <v>64</v>
+      </c>
+      <c r="L194" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="M194" t="n">
+        <v>125.67</v>
+      </c>
+      <c r="N194" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>7</v>
+      </c>
+      <c r="C195" t="n">
         <v>5.986363636363636</v>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D195" t="inlineStr">
         <is>
           <t>Good To Firm</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E195" t="inlineStr">
         <is>
           <t>Turf</t>
         </is>
       </c>
-      <c r="F125" t="n">
-        <v>6</v>
-      </c>
-      <c r="G125" t="n">
+      <c r="F195" t="n">
+        <v>6</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Watchdog</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>3</v>
+      </c>
+      <c r="J195" t="n">
+        <v>135</v>
+      </c>
+      <c r="K195" t="n">
+        <v>65</v>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="n">
+        <v>71.28</v>
+      </c>
+      <c r="N195" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>7</v>
+      </c>
+      <c r="C196" t="n">
+        <v>5.986363636363636</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>6</v>
+      </c>
+      <c r="G196" t="n">
+        <v>2</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Gunalt Wavelength</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>3</v>
+      </c>
+      <c r="J196" t="n">
+        <v>128</v>
+      </c>
+      <c r="K196" t="n">
+        <v>58</v>
+      </c>
+      <c r="L196" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M196" t="n">
+        <v>71.28</v>
+      </c>
+      <c r="N196" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>7</v>
+      </c>
+      <c r="C197" t="n">
+        <v>5.986363636363636</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>6</v>
+      </c>
+      <c r="G197" t="n">
+        <v>3</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Long Shot</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>3</v>
+      </c>
+      <c r="J197" t="n">
+        <v>122</v>
+      </c>
+      <c r="K197" t="n">
+        <v>52</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M197" t="n">
+        <v>71.28</v>
+      </c>
+      <c r="N197" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>7</v>
+      </c>
+      <c r="C198" t="n">
+        <v>5.986363636363636</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>6</v>
+      </c>
+      <c r="G198" t="n">
+        <v>4</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Belling The Cat</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>3</v>
+      </c>
+      <c r="J198" t="n">
+        <v>119</v>
+      </c>
+      <c r="K198" t="n">
+        <v>49</v>
+      </c>
+      <c r="L198" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="M198" t="n">
+        <v>71.28</v>
+      </c>
+      <c r="N198" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>7</v>
+      </c>
+      <c r="C199" t="n">
+        <v>5.986363636363636</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>6</v>
+      </c>
+      <c r="G199" t="n">
+        <v>5</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Auspicious</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>3</v>
+      </c>
+      <c r="J199" t="n">
+        <v>120</v>
+      </c>
+      <c r="K199" t="n">
+        <v>50</v>
+      </c>
+      <c r="L199" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="M199" t="n">
+        <v>71.28</v>
+      </c>
+      <c r="N199" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>7</v>
+      </c>
+      <c r="C200" t="n">
+        <v>5.986363636363636</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>6</v>
+      </c>
+      <c r="G200" t="n">
+        <v>6</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Mystical Land (IRE)</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>3</v>
+      </c>
+      <c r="J200" t="n">
+        <v>128</v>
+      </c>
+      <c r="K200" t="n">
+        <v>58</v>
+      </c>
+      <c r="L200" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="M200" t="n">
+        <v>71.28</v>
+      </c>
+      <c r="N200" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>7</v>
+      </c>
+      <c r="C201" t="n">
+        <v>5.986363636363636</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>6</v>
+      </c>
+      <c r="G201" t="n">
+        <v>7</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Muvable</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>3</v>
+      </c>
+      <c r="J201" t="n">
+        <v>116</v>
+      </c>
+      <c r="K201" t="n">
+        <v>46</v>
+      </c>
+      <c r="L201" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="M201" t="n">
+        <v>71.28</v>
+      </c>
+      <c r="N201" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>REDCAR</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>7</v>
+      </c>
+      <c r="C202" t="n">
+        <v>5.986363636363636</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>6</v>
+      </c>
+      <c r="G202" t="n">
         <v>8</v>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H202" t="inlineStr">
         <is>
           <t>Miss Boyd</t>
         </is>
       </c>
-      <c r="I125" t="n">
-        <v>3</v>
-      </c>
-      <c r="J125" t="n">
+      <c r="I202" t="n">
+        <v>3</v>
+      </c>
+      <c r="J202" t="n">
         <v>117</v>
       </c>
-      <c r="K125" t="n">
+      <c r="K202" t="n">
         <v>47</v>
       </c>
-      <c r="L125" t="n">
+      <c r="L202" t="n">
         <v>13.53</v>
       </c>
-      <c r="M125" t="n">
+      <c r="M202" t="n">
         <v>71.28</v>
       </c>
-      <c r="N125" t="n">
+      <c r="N202" t="n">
         <v>15.3</v>
       </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P125" t="n">
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
         <v>0</v>
       </c>
     </row>
